--- a/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
+++ b/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Close status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Venues" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Revenue" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sky Direct" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Debt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,12 +94,6 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,145 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="115" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>September 2026 close</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>PRELIMINARY — official September 30 SOFR pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>calculation</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Independent full monthly pipeline, compared field-by-field with September 30 API result</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>calculation_code_version</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>c32f25a7ef410eaaf9212b8f546f652c715dc7ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>daily_revision</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>f59c3bc84fc4bf0515022888808ebf87585738396892230c14d8961aa2e9bf5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>monthly_result_sha256</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>3e9c9e13885460b58ffc66c3f481f87f6c7e159a0d8722f20b57a33f95c35df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>daily_result_sha256</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>3e9c9e13885460b58ffc66c3f481f87f6c7e159a0d8722f20b57a33f95c35df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>comparison</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>all result fields match</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>distribution_rewards_workbook_sha256</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>17eee2ca39bd63e68e6d87097ede0007d8741e41cb9a7fceb017da713103b02e</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>distribution_rewards_code</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>1e9ecb2 (merged settle-dr-dune PR #27; finalized September snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>reference_rate_status</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>PRELIMINARY: operator-authorized September 29 SOFR carried to September 30</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -617,228 +475,247 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2" ht="75" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reference-rate assumption</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Operator-authorized SOFR carry-forward: 2026-09-29 rate of 3.88% used for 2026-09-30; not an official observation for that date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Prime side</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue (gross venue yield to prime)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>9011591.411259666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ agent_rate (subproxy USDS / sUSDS yield)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>145157.1728314364</v>
+          <t>prime_agent_revenue (gross venue yield to prime)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>9011591.411259666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>+ agent_rate (subproxy USDS / sUSDS yield)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>145157.1728314364</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>+ distribution_rewards (settle-dr-dune)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>664193.1733497445</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="4" t="n">
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="5" t="n">
         <v>9820941.757440846</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>8214792.081688168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>8214792.081688168</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>3875.849924106662</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>8218667.931612275</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>8214792.081688168</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>8214792.081688168</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>-2042729.752441128</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="5" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>11942.52804365823</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>9011591.411259666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>9011591.411259666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>-8214792.081688168</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="4" t="n">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" s="5" t="n">
         <v>617223.378874959</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-01 → 2026-09-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>arbitrum=510496863, avalanche_c=96488899, base=52011726, ethereum=26093737, optimism=157607011, unichain=60064440</t>
+          <t>2026-09-01 → 2026-09-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01T10:53:23+00:00</t>
+          <t>arbitrum=510496863, avalanche_c=96488899, base=52011726, ethereum=26093737, optimism=157607011, unichain=60064440</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-01T10:53:23+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -869,97 +746,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Period inflow</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>actual_revenue</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>external_revenue</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>revenue (to prime)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>sd_revenue (to Sky)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Avg value</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>CoF alloc</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Profit to Sky</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Profit to Grove</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Utilized Deduction (avg)</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Spread Reimb</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -986,48 +863,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>705318334.5702509</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>771008383.0785193</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>65690048.50826843</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="7" t="n">
         <v>1238436.205059204</v>
       </c>
-      <c r="I2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="n">
+      <c r="I2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7" t="n">
         <v>1238436.205059204</v>
       </c>
-      <c r="K2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6" t="n">
+      <c r="K2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7" t="n">
         <v>727592059.8352032</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="N2" s="7" t="n">
         <v>2058331.348320025</v>
       </c>
-      <c r="O2" s="6" t="n">
+      <c r="O2" s="7" t="n">
         <v>2058331.348320025</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="P2" s="7" t="n">
         <v>-819895.1432608204</v>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1050,46 +928,46 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>682636576.9132075</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>1334095102.952102</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>651458526.0388944</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>2113055.557198851</v>
       </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
+      <c r="I3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7" t="n">
         <v>2113055.557198851</v>
       </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6" t="n">
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7" t="n">
         <v>721405025.8874488</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="N3" s="7" t="n">
         <v>2040828.455379347</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="O3" s="7" t="n">
         <v>2040828.455379347</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="7" t="n">
         <v>72227.10181950497</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" s="7" t="n">
         <v>356306847.9377152</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
@@ -1119,48 +997,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>341638725.767357</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>290670918.976529</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>-50967806.790828</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>829089.790363</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>829089.790363</v>
       </c>
-      <c r="K4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6" t="n">
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7" t="n">
         <v>300922897.595843</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>851299.880442774</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>851299.880442774</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>-22210.09007977402</v>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1183,48 +1062,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>283341073.5577104</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>318369377.9117908</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>35028304.35408038</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>902491.33653301</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="n">
         <v>902491.33653301</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="n">
+      <c r="K5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="n">
         <v>287587439.2492312</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="7" t="n">
         <v>813574.3561080747</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="7" t="n">
         <v>813574.3561080747</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="7" t="n">
         <v>88916.98042493533</v>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1247,48 +1127,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>239105806.766907</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>197178528.746132</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>-41927278.020775</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>1809960</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <v>1809960</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6" t="n">
+      <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="n">
         <v>215035860.3675343</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="7" t="n">
         <v>608328.5907596545</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="7" t="n">
         <v>608328.5907596545</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="7" t="n">
         <v>1201631.409240345</v>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1311,46 +1192,46 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>304282084.3422028</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>273954224.2931706</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>-30327860.04903215</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>588322.3400715282</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
         <v>588322.3400715282</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6" t="n">
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="n">
         <v>193762697.3166503</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="7" t="n">
         <v>548147.5898901902</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="O7" s="7" t="n">
         <v>548147.5898901902</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="7" t="n">
         <v>40174.75018133802</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="7" t="n">
         <v>88817648.89443713</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
@@ -1380,48 +1261,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>251703857.665157</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>96353734.96180294</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>-155350122.703354</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6" t="n">
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="n">
         <v>185386445.524263</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" s="7" t="n">
         <v>524451.4796693093</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="O8" s="7" t="n">
         <v>524451.4796693093</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="7" t="n">
         <v>-524451.4796693093</v>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1444,48 +1326,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>100000199.876674</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>143845442.717366</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>43845242.840692</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>97210.76701900001</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="n">
         <v>97210.76701900001</v>
       </c>
-      <c r="K9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="n">
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
         <v>124073597.0185023</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="7" t="n">
         <v>350999.671848883</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="O9" s="7" t="n">
         <v>350999.671848883</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="7" t="n">
         <v>-253788.904829883</v>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1508,46 +1391,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>100118954.1795337</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>100119291.4453586</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>337.2658248830123</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>402.031314441601</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>402.031314441601</v>
       </c>
-      <c r="K10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="n">
+      <c r="K10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="n">
         <v>58390390.66287698</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" s="7" t="n">
         <v>165184.281380523</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="O10" s="7" t="n">
         <v>165184.281380523</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="7" t="n">
         <v>-164782.2500660814</v>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6" t="n">
+      <c r="Q10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
@@ -1577,48 +1460,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>32509163.72156616</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>77975823.36466382</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>45466659.64309767</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>56044.71251374322</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="n">
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="n">
         <v>56044.71251374322</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="n">
+      <c r="K11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="n">
         <v>25664764.71377946</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>72604.68148813346</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>72604.68148813346</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>-16559.96897439024</v>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1641,48 +1525,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>20321999.31292716</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>20424971.86365957</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="K12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6" t="n">
+      <c r="K12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="n">
         <v>20321999.31292716</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>57490.19341388935</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="7" t="n">
         <v>57490.19341388935</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>45482.35731851836</v>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1705,48 +1590,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>89636603.76011395</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>0.7079334989579819</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>-89636603.05218045</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>51625.38082820114</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="n">
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="n">
         <v>51625.38082820114</v>
       </c>
-      <c r="K13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6" t="n">
+      <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="n">
         <v>14896413.39927341</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="7" t="n">
         <v>42141.40913550332</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="O13" s="7" t="n">
         <v>39685.61177221253</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>9483.971692697811</v>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7" t="n">
         <v>2455.797363290793</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1769,48 +1655,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>6825075.305007</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>26311446.789352</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>19486371.484345</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>37428.204997</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="n">
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>37428.204997</v>
       </c>
-      <c r="K14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6" t="n">
+      <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>13789561.5033751</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>39010.16557054337</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>39010.16557054337</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>-1581.960573543371</v>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1833,48 +1720,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>11021603.25234972</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>39487388.54400175</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>28465785.29165203</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>32690.03755595306</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="n">
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
         <v>32690.03755595306</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6" t="n">
+      <c r="K15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="n">
         <v>10137418.96457929</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="7" t="n">
         <v>28678.38779133129</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="7" t="n">
         <v>28678.38779133129</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n">
         <v>4011.649764621767</v>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1897,46 +1785,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>19999704.07519871</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>19999614.04838496</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6" t="n">
+      <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="K16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6" t="n">
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
         <v>8811902.569257861</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="7" t="n">
         <v>24928.55034832756</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="7" t="n">
         <v>24928.55034832756</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>-25018.57716207674</v>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -1956,46 +1844,48 @@
           <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6" t="n">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7" t="n">
         <v>-9486.73068036744</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6" t="n">
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7" t="n">
         <v>9486.73068036744</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -2025,46 +1915,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>50000607.68881255</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>50000220.37445297</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>-387.3143595855997</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="6" t="n">
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>29635839.11430195</v>
       </c>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6" t="n">
+      <c r="M18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7" t="n">
         <v>29635839.11430195</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -2094,48 +1984,49 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>40137.360529</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>1.367235</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>-40135.993294</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6" t="n">
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="n">
         <v>255930.9107552667</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="7" t="n">
         <v>724.0191938474095</v>
       </c>
-      <c r="O19" s="6" t="n">
+      <c r="O19" s="7" t="n">
         <v>724.0191938474095</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="7" t="n">
         <v>-724.0191938474095</v>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2158,48 +2049,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6" t="n">
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
         <v>1468.586624033333</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="7" t="n">
         <v>4.154577891704791</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="7" t="n">
         <v>4.154577891704791</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>-4.154577891704791</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2222,48 +2114,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>2.08</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>2.03</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>-0.05</v>
       </c>
-      <c r="H21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6" t="n">
+      <c r="H21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="n">
         <v>962.4027748666666</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="7" t="n">
         <v>2.722602280276279</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="7" t="n">
         <v>2.722602280276279</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>-2.722602280276279</v>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2286,48 +2179,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>907.5387997189844</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>1091.224531135664</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6" t="n">
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="K22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6" t="n">
+      <c r="K22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7" t="n">
         <v>907.5387997189844</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="7" t="n">
         <v>2.567394099519739</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="7" t="n">
         <v>2.567394099519739</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="7" t="n">
         <v>181.1183373171599</v>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2350,48 +2244,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6" t="n">
+      <c r="G23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="7" t="n">
         <v>0.8031349423342302</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="7" t="n">
         <v>0.8031349423342302</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="7" t="n">
         <v>-0.8031349423342302</v>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2414,48 +2309,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6" t="n">
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
         <v>178.3188656666667</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="7" t="n">
         <v>0.5044575545281519</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="7" t="n">
         <v>0.5044575545281519</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="7" t="n">
         <v>-0.5044575545281519</v>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2478,48 +2374,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>3039.891609</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>-3039.891609</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6" t="n">
+      <c r="H25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="n">
         <v>146.7413761333333</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="7" t="n">
         <v>0.415125990598731</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="7" t="n">
         <v>0.415125990598731</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="7" t="n">
         <v>-0.415125990598731</v>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2542,48 +2439,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>100.8102461380194</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>101.2017120368429</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="n">
+      <c r="I26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="K26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6" t="n">
+      <c r="K26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7" t="n">
         <v>100.8102461380194</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="7" t="n">
         <v>0.2851885023384411</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="7" t="n">
         <v>0.2851885023384411</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="7" t="n">
         <v>0.1062773964850405</v>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2606,48 +2504,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>22.16728989737678</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>22.1674058733521</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="n">
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="K27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6" t="n">
+      <c r="K27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="n">
         <v>22.16728989737678</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="7" t="n">
         <v>0.06271045304343052</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="7" t="n">
         <v>0.06271045304343052</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="7" t="n">
         <v>-0.06259447706810667</v>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2670,48 +2569,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>5.953731</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>5.971376</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>0.017645</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>0.017645</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6" t="n">
+      <c r="I28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7" t="n">
         <v>0.017645</v>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6" t="n">
+      <c r="K28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="n">
         <v>5.953731</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="7" t="n">
         <v>0.01684288742724925</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="7" t="n">
         <v>0.01684288742724925</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="7" t="n">
         <v>0.0008021125727507489</v>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2734,48 +2634,49 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>3.882840172509015</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>3.88330436564981</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="n">
+      <c r="I29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="K29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6" t="n">
+      <c r="K29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="n">
         <v>3.882840172509015</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" s="7" t="n">
         <v>0.01098441295442646</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="O29" s="7" t="n">
         <v>0.01098441295442646</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="7" t="n">
         <v>-0.01052021981363122</v>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2798,46 +2699,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>0.8392619557395509</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>0.009413515804298108</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K30" s="7" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="7" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="M30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="6" t="n">
+      <c r="M30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="7" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="P30" s="7" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
@@ -2867,48 +2768,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>1.762330143465235</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>1.766602634051488</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6" t="n">
+      <c r="I31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="K31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6" t="n">
+      <c r="K31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" t="n">
         <v>1.762330143465235</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="7" t="n">
         <v>0.004985567573683288</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="7" t="n">
         <v>0.004985567573683288</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="7" t="n">
         <v>-0.0007130769874298964</v>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2931,48 +2833,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>0.156574</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>0.157194</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>0.00062</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>0.00062</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6" t="n">
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
         <v>0.00062</v>
       </c>
-      <c r="K32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="6" t="n">
+      <c r="K32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" t="n">
         <v>0.156574</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" s="7" t="n">
         <v>0.0004429421241964281</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="O32" s="7" t="n">
         <v>0.0004429421241964281</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P32" s="7" t="n">
         <v>0.0001770578758035719</v>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2995,48 +2898,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="6" t="n">
+      <c r="E33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" t="n">
         <v>0.1180892666666667</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="7" t="n">
         <v>0.0003340702199735064</v>
       </c>
-      <c r="O33" s="6" t="n">
+      <c r="O33" s="7" t="n">
         <v>0.0003340702199735064</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="7" t="n">
         <v>-0.0003340702199735064</v>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3059,48 +2963,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>0.058479</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>0.058664</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>0.000185</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>0.000185</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="n">
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
         <v>0.000185</v>
       </c>
-      <c r="K34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="6" t="n">
+      <c r="K34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7" t="n">
         <v>0.058479</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" s="7" t="n">
         <v>0.0001654349539571252</v>
       </c>
-      <c r="O34" s="6" t="n">
+      <c r="O34" s="7" t="n">
         <v>0.0001654349539571252</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="P34" s="7" t="n">
         <v>1.95650460428748e-05</v>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3123,48 +3028,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>0.006402</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>0.006417</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="I35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="6" t="n">
+      <c r="I35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="7" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="K35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="6" t="n">
+      <c r="K35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="n">
         <v>0.006402</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="7" t="n">
         <v>1.811102404681194e-05</v>
       </c>
-      <c r="O35" s="6" t="n">
+      <c r="O35" s="7" t="n">
         <v>1.811102404681194e-05</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="P35" s="7" t="n">
         <v>-3.111024046811941e-06</v>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3187,48 +3093,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>0.005749186661712982</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>0.005749998097404683</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="I36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="6" t="n">
+      <c r="I36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="7" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="K36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="6" t="n">
+      <c r="K36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7" t="n">
         <v>0.005749186661712982</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="7" t="n">
         <v>1.626423896905565e-05</v>
       </c>
-      <c r="O36" s="6" t="n">
+      <c r="O36" s="7" t="n">
         <v>1.626423896905565e-05</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="P36" s="7" t="n">
         <v>-1.545280327735465e-05</v>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3251,48 +3158,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>0.001719</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>0.001724</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <v>5e-06</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="7" t="n">
         <v>5e-06</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6" t="n">
+      <c r="I37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7" t="n">
         <v>5e-06</v>
       </c>
-      <c r="K37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="6" t="n">
+      <c r="K37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="n">
         <v>0.001719</v>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="7" t="n">
         <v>4.862988181266749e-06</v>
       </c>
-      <c r="O37" s="6" t="n">
+      <c r="O37" s="7" t="n">
         <v>4.862988181266749e-06</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="P37" s="7" t="n">
         <v>1.37011818733251e-07</v>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3315,48 +3223,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="6" t="n">
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="7" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="7" t="n">
         <v>3.508323953316347e-06</v>
       </c>
-      <c r="O38" s="6" t="n">
+      <c r="O38" s="7" t="n">
         <v>3.508323953316347e-06</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="P38" s="7" t="n">
         <v>-3.508323953316347e-06</v>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3379,48 +3288,49 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>0.000522802561158111</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>0.000523116949023306</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="I39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="n">
+      <c r="I39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="K39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="6" t="n">
+      <c r="K39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7" t="n">
         <v>0.000522802561158111</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="7" t="n">
         <v>1.47898934034199e-06</v>
       </c>
-      <c r="O39" s="6" t="n">
+      <c r="O39" s="7" t="n">
         <v>1.47898934034199e-06</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="7" t="n">
         <v>-1.16460147514699e-06</v>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3443,48 +3353,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="6" t="n">
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="7" t="n">
         <v>2.118788275229259e-07</v>
       </c>
-      <c r="O40" s="6" t="n">
+      <c r="O40" s="7" t="n">
         <v>2.118788275229259e-07</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="P40" s="7" t="n">
         <v>-2.118788275229259e-07</v>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3507,48 +3418,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>1.18094e-06</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>1.185745e-06</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="7" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="6" t="n">
+      <c r="I41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="7" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="K41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="6" t="n">
+      <c r="K41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7" t="n">
         <v>1.18094e-06</v>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="7" t="n">
         <v>3.340836104005325e-09</v>
       </c>
-      <c r="O41" s="6" t="n">
+      <c r="O41" s="7" t="n">
         <v>3.340836104005325e-09</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="7" t="n">
         <v>1.464163895994674e-09</v>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3571,48 +3483,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="7" t="n">
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3635,48 +3548,49 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="7" t="n">
+      <c r="E43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3699,48 +3613,49 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="7" t="n">
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3763,46 +3678,46 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="6" t="n">
+      <c r="E45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
@@ -3832,48 +3747,49 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="7" t="n">
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3896,48 +3812,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="n">
+      <c r="E47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="n">
         <v>984135</v>
       </c>
-      <c r="I47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="6" t="n">
+      <c r="I47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="7" t="n">
         <v>984135</v>
       </c>
-      <c r="K47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="7" t="n">
+      <c r="K47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="6" t="n">
+      <c r="N47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="7" t="n">
         <v>984135</v>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3960,48 +3877,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="7" t="n">
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4024,46 +3942,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="6" t="n">
+      <c r="E49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
@@ -4093,48 +4011,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="7" t="n">
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4157,46 +4076,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6" t="n">
+      <c r="E51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7" t="n">
         <v>1778866.820550583</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="7" t="n">
         <v>1778866.820550583</v>
       </c>
-      <c r="H51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="6" t="n">
+      <c r="H51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="7" t="n">
         <v>296477.8034250973</v>
       </c>
-      <c r="M51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="6" t="n">
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="7" t="n">
         <v>296477.8034250973</v>
       </c>
-      <c r="R51" s="6" t="n">
+      <c r="R51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
@@ -4226,48 +4145,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="7" t="n">
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4290,46 +4210,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="7" t="n">
         <v>99326272.7790609</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G53" s="7" t="n">
         <v>9326272.7790609</v>
       </c>
-      <c r="H53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="6" t="n">
+      <c r="H53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="7" t="n">
         <v>91554378.79651015</v>
       </c>
-      <c r="M53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="6" t="n">
+      <c r="M53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="7" t="n">
         <v>91554378.79651015</v>
       </c>
-      <c r="R53" s="6" t="n">
+      <c r="R53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
@@ -4359,48 +4279,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
+      <c r="E54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4423,46 +4344,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
+      <c r="E55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
@@ -4492,48 +4413,49 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="7" t="n">
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4556,46 +4478,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
+      <c r="E57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
@@ -4625,48 +4547,49 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4679,46 +4602,48 @@
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="6" t="n">
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
@@ -4728,39 +4653,39 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
@@ -4787,10 +4712,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>309261582.801972</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>300586529.588196</v>
       </c>
     </row>
@@ -4815,10 +4740,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>367530003.125796</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>447000057.62485</v>
       </c>
     </row>
@@ -4843,10 +4768,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>230753.271254</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="7" t="n">
         <v>31037.026892</v>
       </c>
     </row>
@@ -4871,20 +4796,24 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>9475726.147763001</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="7" t="n">
         <v>8678568.642703</v>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="5" t="inlineStr">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="F67" s="9" t="n">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4893,7 +4822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4914,19 +4843,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -4938,7 +4867,7 @@
           <t>Time-weighted utilized</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>2687080256.868631</v>
       </c>
     </row>
@@ -4948,7 +4877,7 @@
           <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>1000000000</v>
       </c>
     </row>
@@ -4958,7 +4887,7 @@
           <t xml:space="preserve">  — excess (full base-rate tranche)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>1687080256.868631</v>
       </c>
     </row>
@@ -4968,7 +4897,7 @@
           <t>Base rate (BR_apr = apy_to_apr(SSR,12) + spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>0.03737387237537716</v>
       </c>
     </row>
@@ -4978,7 +4907,7 @@
           <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>0.03748</v>
       </c>
     </row>
@@ -4988,37 +4917,37 @@
           <t>Subsidised rate (BR*), period avg</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>0.03703300982840613</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Effective blended rate charged</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>0.03724932945187823</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Diff vs base rate (bps)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>-1.245429234989398</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Subsidy benefit to prime (USD)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>27506.04089315324</v>
       </c>
     </row>
@@ -5028,7 +4957,7 @@
           <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>8254240.650624979</v>
       </c>
     </row>
@@ -5038,32 +4967,32 @@
           <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>8226734.609731826</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  = subsidy benefit</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>27506.04089315324</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Avg balance</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>CoF (USD)</t>
         </is>
@@ -5075,10 +5004,10 @@
           <t>Subsidised (first $1B)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>1000000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>3043809.026992285</v>
       </c>
     </row>
@@ -5088,20 +5017,20 @@
           <t>Excess (&gt; cap)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>1687080256.868631</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>5182925.58273954</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -5113,7 +5042,7 @@
           <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>8214792.081688168</v>
       </c>
     </row>
@@ -5123,7 +5052,7 @@
           <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>3875.849924106662</v>
       </c>
     </row>
@@ -5133,24 +5062,24 @@
           <t>equals sky_revenue (total Sky take this month)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>8218667.931612275</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="4" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>
@@ -5160,7 +5089,7 @@
           <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="4" t="n">
         <v>8214792.081688168</v>
       </c>
     </row>
@@ -5170,34 +5099,34 @@
           <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="4" t="n">
         <v>-2042729.752441128</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="4" t="n">
         <v>11942.52804365823</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -5221,7 +5150,7 @@
           <t>cap_usd</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="7" t="n">
         <v>1000000000</v>
       </c>
     </row>
@@ -5272,7 +5201,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
@@ -5284,7 +5213,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Base rate composition: base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). Daily charge = utilized_d x base_apr / 365 — no intra-month compounding.</t>
         </is>
@@ -5295,7 +5224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5324,52 +5253,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Cap (USD)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Active?</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>actual_revenue</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>sd_revenue (to Sky)</t>
         </is>
@@ -5386,6 +5315,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>2025-10-30</t>
@@ -5411,10 +5341,10 @@
           <t>USTB on Eth</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5429,6 +5359,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>2025-11-13</t>
@@ -5454,10 +5385,10 @@
           <t>USDT in sUSDS/USDT Curve</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="7" t="n">
         <v>0.008700428167360377</v>
       </c>
     </row>
@@ -5472,6 +5403,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-02-01</t>
@@ -5497,10 +5429,10 @@
           <t>USDT in USDT/USDS Uniswap V4</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>3875.841223678495</v>
       </c>
     </row>
@@ -5509,7 +5441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5543,83 +5475,83 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). sub_apr applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apr.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>cum_debt</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>− ALM idle</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>− PSM USDS</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>− SDE NAV</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>− Curve idle</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>− Lending idle</t>
         </is>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <f> utilized</f>
         <v/>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>SSR APY</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>base APR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>T (months)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>ref_rate APR</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>sub APR</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>daily Sky charge</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>daily Sky charge (gross on cum_debt)</t>
         </is>
@@ -5631,46 +5563,46 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>2906763421.062537</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>10787782.10438779</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>46184868.72615942</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>66134186.85567197</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>321674890.8327978</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>2371981692.54352</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>0.03519999850777533</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>0.03664455749990904</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="8" t="n">
         <v>0.0366</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>0.03661485249996968</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="4" t="n">
         <v>238056.2041676801</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="4" t="n">
         <v>291746.1762241619</v>
       </c>
     </row>
@@ -5680,46 +5612,46 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>2890435099.376095</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>10783394.72011987</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>42941079.57266001</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>73873920.36187291</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>316351823.6700861</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>2356484881.051357</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>0.03519999850777533</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>0.03664455749990904</v>
       </c>
       <c r="K7" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="8" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>0.03654818583330301</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="4" t="n">
         <v>236317.7371362924</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="4" t="n">
         <v>289924.2288554427</v>
       </c>
     </row>
@@ -5729,46 +5661,46 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>2967508830.591976</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>10781425.15239475</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>33590920.91094027</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>85998904.9177648</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>336540318.0229259</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>2410597261.58795</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="8" t="n">
         <v>0.0366</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>0.03687310577117104</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="4" t="n">
         <v>245634.7734358992</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="4" t="n">
         <v>302728.6110143323</v>
       </c>
     </row>
@@ -5778,46 +5710,46 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>2988013324.706798</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>10779506.1219177</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>28343954.51391455</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>88309100.01729183</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>342696670.1153459</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>2427884093.938328</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="8" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="4" t="n">
         <v>247224.3482260297</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O9" s="4" t="n">
         <v>304648.0562334253</v>
       </c>
     </row>
@@ -5827,46 +5759,46 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>2928274110.318439</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>10777287.92069298</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>33362192.54020159</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>82344906.19469523</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>327280160.0470022</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>2384509563.615847</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="8" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="4" t="n">
         <v>242777.648737094</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="4" t="n">
         <v>298523.6709751842</v>
       </c>
     </row>
@@ -5876,46 +5808,46 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>2956412327.73415</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>10787280.79874208</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>35799400.42037193</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>77757918.74799147</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>330059413.61901</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>2412008314.148035</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="8" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="4" t="n">
         <v>245596.7842765161</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" s="4" t="n">
         <v>301408.3638138557</v>
       </c>
     </row>
@@ -5925,46 +5857,46 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>3000452982.63504</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>10784103.99660763</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>39204009.08141842</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>73468764.68268934</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>341972638.172222</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>2445023466.702103</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="8" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="4" t="n">
         <v>248981.4540561729</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="4" t="n">
         <v>305923.3535136677</v>
       </c>
     </row>
@@ -5974,46 +5906,46 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>2995839152.421766</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>10782756.13469957</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>37651547.86163576</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>77135483.14091809</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>345474185.8099677</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>2434795179.474545</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="8" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="4" t="n">
         <v>247750.2151739581</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="O13" s="4" t="n">
         <v>305267.7013398379</v>
       </c>
     </row>
@@ -6023,46 +5955,46 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>3133651114.325167</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>10797020.24891723</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>40743786.39046462</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>74412072.93470116</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>383589267.5591224</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>2534108967.191961</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="8" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="4" t="n">
         <v>257931.7333553413</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="4" t="n">
         <v>319396.0014276766</v>
       </c>
     </row>
@@ -6072,46 +6004,46 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>3227081891.544717</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>10846682.58683929</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>42457056.322888</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>75494030.84493366</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>421499085.0281916</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>2586785036.761865</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="4" t="n">
         <v>262966.717543647</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="4" t="n">
         <v>328609.1043490277</v>
       </c>
     </row>
@@ -6121,46 +6053,46 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>3297373641.594151</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>11051222.40951546</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>39392044.00456543</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>70852872.02856682</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>448108701.9685125</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>2637968801.182991</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="4" t="n">
         <v>268214.0093852202</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O16" s="4" t="n">
         <v>335815.3216082659</v>
       </c>
     </row>
@@ -6170,46 +6102,46 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="7" t="n">
         <v>3261296362.641112</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>10958189.66850853</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>38323346.1236461</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>74526830.75221506</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>439333902.4873285</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>2608154093.609414</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K17" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="4" t="n">
         <v>265157.444992603</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O17" s="4" t="n">
         <v>332116.7266796306</v>
       </c>
     </row>
@@ -6219,46 +6151,46 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="7" t="n">
         <v>3271620408.368682</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>10967668.13417339</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>44209251.24223101</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>69262929.5670072</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>438574487.8959026</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>2618606071.529368</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="4" t="n">
         <v>266228.9679469608</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="4" t="n">
         <v>333175.1341948064</v>
       </c>
     </row>
@@ -6268,46 +6200,46 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="7" t="n">
         <v>3336773639.899233</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>11011831.47225842</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>38717183.1975746</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>74780064.69773053</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>459982093.6032678</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>2662282466.928402</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="4" t="n">
         <v>270706.6142443497</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" s="4" t="n">
         <v>339854.5573308132</v>
       </c>
     </row>
@@ -6317,46 +6249,46 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>3408882342.468478</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>11013377.08004701</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>51464357.30621822</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>63078762.22766157</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>486544767.4335539</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>2706781078.420998</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="8" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="4" t="n">
         <v>275633.8498519812</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="4" t="n">
         <v>347612.3429632451</v>
       </c>
     </row>
@@ -6366,46 +6298,46 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>3472868914.590904</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>11015189.69398859</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>53285053.35791527</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>59219558.5191095</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>520256687.5533239</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>2739092425.466567</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="8" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="4" t="n">
         <v>278581.0696179863</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" s="4" t="n">
         <v>353806.8649159018</v>
       </c>
     </row>
@@ -6415,46 +6347,46 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>3532508643.580109</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>11015476.02521076</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>54701824.10007302</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>56533917.02449908</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>544096705.3514518</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>2776160721.078874</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K22" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="4" t="n">
         <v>284608.3258503062</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="4" t="n">
         <v>362148.1146489092</v>
       </c>
     </row>
@@ -6464,46 +6396,46 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>3557227409.970616</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>11011283.2026294</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>39807184.62271105</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>75881936.86035079</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>547009412.1599061</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>2793517593.125018</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="4" t="n">
         <v>286387.7294192506</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" s="4" t="n">
         <v>364682.2498904572</v>
       </c>
     </row>
@@ -6513,46 +6445,46 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="7" t="n">
         <v>3582188103.687335</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>11022797.04070983</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>42362026.83740311</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>69117035.89852072</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>555046298.1893152</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>2814639945.721386</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="4" t="n">
         <v>288553.1650746243</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="4" t="n">
         <v>367241.1872015567</v>
       </c>
     </row>
@@ -6562,46 +6494,46 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="7" t="n">
         <v>3615656122.574477</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>11021528.4331681</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>40669150.95574692</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>70044162.34119777</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>555099974.3238693</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <v>2848821306.520495</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="4" t="n">
         <v>292057.3929813354</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" s="4" t="n">
         <v>370672.2842387968</v>
       </c>
     </row>
@@ -6611,46 +6543,46 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="7" t="n">
         <v>3668718424.821697</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>11017474.21178086</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>39640105.26414733</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>80565486.31273285</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>511522523.5145142</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>2935972835.518521</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="4" t="n">
         <v>300992.0524825271</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="4" t="n">
         <v>376112.1612940687</v>
       </c>
     </row>
@@ -6660,46 +6592,46 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="7" t="n">
         <v>3654567772.917019</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>11013549.04707003</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>38195404.07725928</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>77310138.73431022</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>509580863.5732393</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>2928467817.485141</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K27" t="n">
         <v>8</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="8" t="n">
         <v>0.0387</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="4" t="n">
         <v>300222.6479585964</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" s="4" t="n">
         <v>374661.4551740298</v>
       </c>
     </row>
@@ -6709,46 +6641,46 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="7" t="n">
         <v>3613986960.44891</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>11024090.25538417</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>38791154.5504749</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>77315744.47759701</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>489850897.9694406</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>2907005073.196013</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K28" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="L28" s="8" t="n">
         <v>0.0387</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="4" t="n">
         <v>298022.3157970248</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="O28" s="4" t="n">
         <v>370501.1639450316</v>
       </c>
     </row>
@@ -6758,46 +6690,46 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <v>3562391445.516993</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>11106742.99290403</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>42557094.58933863</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>72747259.58101186</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>476137012.6093084</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>2869843335.74443</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="8" t="n">
         <v>0.0388</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="4" t="n">
         <v>294212.5436172377</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" s="4" t="n">
         <v>365211.6599856028</v>
       </c>
     </row>
@@ -6807,46 +6739,46 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="7" t="n">
         <v>3562110063.464996</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>11105892.44404138</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>39434498.72772756</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>78636692.55074844</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>477489965.700973</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>2865443014.041506</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K30" t="n">
         <v>8</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="8" t="n">
         <v>0.039</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="4" t="n">
         <v>293761.4284553658</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O30" s="4" t="n">
         <v>365182.8130697398</v>
       </c>
     </row>
@@ -6856,46 +6788,46 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="7" t="n">
         <v>3556747626.534367</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="7" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>0.9981644656134642</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>40058756.90344783</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>75811953.01965727</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>476178335.913344</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <v>2863593440.100142</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="J31" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K31" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" s="8" t="n">
         <v>0.039</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="4" t="n">
         <v>293571.8125808269</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="4" t="n">
         <v>364633.0631270524</v>
       </c>
     </row>
@@ -6905,46 +6837,46 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="7" t="n">
         <v>3569305881.745206</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="7" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>348.044919387507</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>40276114.07045595</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>77458558.38944019</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>478099948.9814835</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>2872365772.659295</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="8" t="n">
         <v>0.039</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="4" t="n">
         <v>294471.1405140067</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="4" t="n">
         <v>365920.51884387</v>
       </c>
     </row>
@@ -6954,46 +6886,46 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="7" t="n">
         <v>3607683503.927528</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C33" s="7" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>475.1354724600163</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>49030490.46679787</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>66105314.46354181</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>489068699.5676167</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>2902373384.694488</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="J33" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="8" t="n">
         <v>0.039</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="4" t="n">
         <v>297547.4812169262</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" s="4" t="n">
         <v>369854.9419183315</v>
       </c>
     </row>
@@ -7003,46 +6935,46 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="7" t="n">
         <v>3630529651.948061</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="7" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>39645.63435542155</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>46729012.84603118</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>70493387.35718162</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>490680595.5793573</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>2921481870.931524</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K34" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L34" s="8" t="n">
         <v>0.0388</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="4" t="n">
         <v>299506.457956336</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="4" t="n">
         <v>372197.098800994</v>
       </c>
     </row>
@@ -7052,59 +6984,71 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="7" t="n">
         <v>3686615117.414475</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="7" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>125648.5335501426</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>52072873.79227647</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>63718676.68799376</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>493934577.7121899</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>2975658201.088854</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="8" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K35" t="n">
         <v>8</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" s="8" t="n">
         <v>0.0388</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="4" t="n">
         <v>305060.54367973</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" s="4" t="n">
         <v>377946.9065515799</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>
       </c>
-      <c r="N37" s="12" t="n">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="13" t="n">
         <v>8226734.609731826</v>
       </c>
-      <c r="O37" s="12" t="n">
+      <c r="O37" s="13" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>

--- a/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
+++ b/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Close status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Venues" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Revenue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sky Direct" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Debt" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,12 +77,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -94,6 +92,12 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,7 +465,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>September 2026 close</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Official reference-rate coverage complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Reference-rate-only recalculation of saved independently validated monthly inputs; compared with September 30 API result</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>calculation_code_version</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>c32f25a7ef410eaaf9212b8f546f652c715dc7ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>daily_revision</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>08ed233241c4ed1750dde86085a7bc5a0fff028fd08db4b1ca091956c283f645</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>monthly_result_sha256</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>72d23df466c98cf2f45f1c0b72aefd1fc7c9c0579d306de41b4350994c4a95ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>daily_result_sha256</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>72d23df466c98cf2f45f1c0b72aefd1fc7c9c0579d306de41b4350994c4a95ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>all result fields match</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>distribution_rewards_workbook_sha256</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>17eee2ca39bd63e68e6d87097ede0007d8741e41cb9a7fceb017da713103b02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>distribution_rewards_code</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>1e9ecb2 (merged settle-dr-dune PR #27; finalized September snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>reference_rate_status</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>official coverage complete</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -475,247 +617,228 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="75" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Reference-rate assumption</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Operator-authorized SOFR carry-forward: 2026-09-29 rate of 3.88% used for 2026-09-30; not an official observation for that date.</t>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Prime side</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Prime side</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>prime_agent_revenue (gross venue yield to prime)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>9011591.411259666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>prime_agent_revenue (gross venue yield to prime)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>9011591.411259666</v>
+          <t>+ agent_rate (subproxy USDS / sUSDS yield)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>145157.1728314364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>+ agent_rate (subproxy USDS / sUSDS yield)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>145157.1728314364</v>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>664193.1733497445</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>+ distribution_rewards (settle-dr-dune)</t>
-        </is>
-      </c>
       <c r="B7" s="4" t="n">
-        <v>664193.1733497445</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" s="5" t="n">
         <v>9820941.757440846</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sky side</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Sky side</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>8214792.081688168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
+          <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3875.849924106662</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="n">
+        <v>8218667.931612275</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>8214792.081688168</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>3875.849924106662</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" s="5" t="n">
-        <v>8218667.931612275</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>8214792.081688168</v>
+          <t>reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-2042729.752441128</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>reduction from idle/SDE deductions</t>
-        </is>
-      </c>
       <c r="B17" s="4" t="n">
-        <v>-2042729.752441128</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" s="5" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B19" s="3" t="n">
         <v>11942.52804365823</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Comparison (Grove-style "Profit to Grove")</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Comparison (Grove-style "Profit to Grove")</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>9011591.411259666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>9011591.411259666</v>
+          <t>− CoF (deducted per-venue in display)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-8214792.081688168</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>− CoF (deducted per-venue in display)</t>
-        </is>
-      </c>
       <c r="B24" s="4" t="n">
-        <v>-8214792.081688168</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" s="5" t="n">
         <v>617223.378874959</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-01 → 2026-09-30 (30 days)</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 → 2026-09-30 (30 days)</t>
+          <t>arbitrum=510496863, avalanche_c=96488899, base=52011726, ethereum=26093737, optimism=157607011, unichain=60064440</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Generated</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>arbitrum=510496863, avalanche_c=96488899, base=52011726, ethereum=26093737, optimism=157607011, unichain=60064440</t>
+          <t>2026-10-01T15:36:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-01T10:53:23+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>0.1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -746,97 +869,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Period inflow</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>actual_revenue</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>external_revenue</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>revenue (to prime)</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>sd_revenue (to Sky)</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Avg value</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>CoF alloc</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Profit to Sky</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Profit to Grove</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Utilized Deduction (avg)</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Spread Reimb</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -863,49 +986,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="6" t="n">
         <v>705318334.5702509</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="6" t="n">
         <v>771008383.0785193</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="6" t="n">
         <v>65690048.50826843</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="6" t="n">
         <v>1238436.205059204</v>
       </c>
-      <c r="I2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7" t="n">
+      <c r="I2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>1238436.205059204</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7" t="n">
+      <c r="K2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="n">
         <v>727592059.8352032</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="N2" s="6" t="n">
         <v>2058331.348320025</v>
       </c>
-      <c r="O2" s="7" t="n">
+      <c r="O2" s="6" t="n">
         <v>2058331.348320025</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="P2" s="6" t="n">
         <v>-819895.1432608204</v>
       </c>
-      <c r="Q2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -928,46 +1050,46 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="6" t="n">
         <v>682636576.9132075</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="6" t="n">
         <v>1334095102.952102</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="6" t="n">
         <v>651458526.0388944</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="6" t="n">
         <v>2113055.557198851</v>
       </c>
-      <c r="I3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7" t="n">
+      <c r="I3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6" t="n">
         <v>2113055.557198851</v>
       </c>
-      <c r="K3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7" t="n">
+      <c r="K3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6" t="n">
         <v>721405025.8874488</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="N3" s="6" t="n">
         <v>2040828.455379347</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="O3" s="6" t="n">
         <v>2040828.455379347</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="P3" s="6" t="n">
         <v>72227.10181950497</v>
       </c>
-      <c r="Q3" s="7" t="n">
+      <c r="Q3" s="6" t="n">
         <v>356306847.9377152</v>
       </c>
-      <c r="R3" s="7" t="n">
+      <c r="R3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
@@ -997,49 +1119,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="6" t="n">
         <v>341638725.767357</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="6" t="n">
         <v>290670918.976529</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="6" t="n">
         <v>-50967806.790828</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="6" t="n">
         <v>829089.790363</v>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>829089.790363</v>
       </c>
-      <c r="K4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7" t="n">
+      <c r="K4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="n">
         <v>300922897.595843</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="6" t="n">
         <v>851299.880442774</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="6" t="n">
         <v>851299.880442774</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="P4" s="6" t="n">
         <v>-22210.09007977402</v>
       </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1062,49 +1183,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="6" t="n">
         <v>283341073.5577104</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="6" t="n">
         <v>318369377.9117908</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="6" t="n">
         <v>35028304.35408038</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="6" t="n">
         <v>902491.33653301</v>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="n">
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>902491.33653301</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="n">
+      <c r="K5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6" t="n">
         <v>287587439.2492312</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="6" t="n">
         <v>813574.3561080747</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="O5" s="6" t="n">
         <v>813574.3561080747</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="P5" s="6" t="n">
         <v>88916.98042493533</v>
       </c>
-      <c r="Q5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1127,49 +1247,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="6" t="n">
         <v>239105806.766907</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>197178528.746132</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>-41927278.020775</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="6" t="n">
         <v>1809960</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7" t="n">
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>1809960</v>
       </c>
-      <c r="K6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7" t="n">
+      <c r="K6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>215035860.3675343</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="N6" s="6" t="n">
         <v>608328.5907596545</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="O6" s="6" t="n">
         <v>608328.5907596545</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="P6" s="6" t="n">
         <v>1201631.409240345</v>
       </c>
-      <c r="Q6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1192,46 +1311,46 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="6" t="n">
         <v>304282084.3422028</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>273954224.2931706</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="6" t="n">
         <v>-30327860.04903215</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="6" t="n">
         <v>588322.3400715282</v>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>588322.3400715282</v>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="n">
+      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>193762697.3166503</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="N7" s="6" t="n">
         <v>548147.5898901902</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="O7" s="6" t="n">
         <v>548147.5898901902</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="P7" s="6" t="n">
         <v>40174.75018133802</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="Q7" s="6" t="n">
         <v>88817648.89443713</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="R7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
@@ -1261,49 +1380,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="6" t="n">
         <v>251703857.665157</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>96353734.96180294</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>-155350122.703354</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="n">
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>185386445.524263</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="N8" s="6" t="n">
         <v>524451.4796693093</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="6" t="n">
         <v>524451.4796693093</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="P8" s="6" t="n">
         <v>-524451.4796693093</v>
       </c>
-      <c r="Q8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1326,49 +1444,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="6" t="n">
         <v>100000199.876674</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="6" t="n">
         <v>143845442.717366</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="6" t="n">
         <v>43845242.840692</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="6" t="n">
         <v>97210.76701900001</v>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7" t="n">
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>97210.76701900001</v>
       </c>
-      <c r="K9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7" t="n">
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>124073597.0185023</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="N9" s="6" t="n">
         <v>350999.671848883</v>
       </c>
-      <c r="O9" s="7" t="n">
+      <c r="O9" s="6" t="n">
         <v>350999.671848883</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="P9" s="6" t="n">
         <v>-253788.904829883</v>
       </c>
-      <c r="Q9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="Q9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1391,46 +1508,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="6" t="n">
         <v>100118954.1795337</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>100119291.4453586</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>337.2658248830123</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="6" t="n">
         <v>402.031314441601</v>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7" t="n">
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>402.031314441601</v>
       </c>
-      <c r="K10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="7" t="n">
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>58390390.66287698</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="N10" s="6" t="n">
         <v>165184.281380523</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="6" t="n">
         <v>165184.281380523</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="P10" s="6" t="n">
         <v>-164782.2500660814</v>
       </c>
-      <c r="Q10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7" t="n">
+      <c r="Q10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
@@ -1460,49 +1577,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>32509163.72156616</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>77975823.36466382</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>45466659.64309767</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>56044.71251374322</v>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7" t="n">
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>56044.71251374322</v>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7" t="n">
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>25664764.71377946</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="6" t="n">
         <v>72604.68148813346</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <v>72604.68148813346</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>-16559.96897439024</v>
       </c>
-      <c r="Q11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="Q11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1525,49 +1641,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>20321999.31292716</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>20424971.86365957</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7" t="n">
+      <c r="I12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>102972.5507324077</v>
       </c>
-      <c r="K12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="n">
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>20321999.31292716</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="6" t="n">
         <v>57490.19341388935</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <v>57490.19341388935</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>45482.35731851836</v>
       </c>
-      <c r="Q12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1590,49 +1705,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>89636603.76011395</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>0.7079334989579819</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>-89636603.05218045</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>51625.38082820114</v>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7" t="n">
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="n">
         <v>51625.38082820114</v>
       </c>
-      <c r="K13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7" t="n">
+      <c r="K13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>14896413.39927341</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N13" s="6" t="n">
         <v>42141.40913550332</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <v>39685.61177221253</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>9483.971692697811</v>
       </c>
-      <c r="Q13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7" t="n">
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
         <v>2455.797363290793</v>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1655,49 +1769,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>6825075.305007</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>26311446.789352</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>19486371.484345</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>37428.204997</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7" t="n">
+      <c r="I14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6" t="n">
         <v>37428.204997</v>
       </c>
-      <c r="K14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7" t="n">
+      <c r="K14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>13789561.5033751</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="6" t="n">
         <v>39010.16557054337</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <v>39010.16557054337</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>-1581.960573543371</v>
       </c>
-      <c r="Q14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1720,49 +1833,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>11021603.25234972</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>39487388.54400175</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>28465785.29165203</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="6" t="n">
         <v>32690.03755595306</v>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
+      <c r="I15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>32690.03755595306</v>
       </c>
-      <c r="K15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="7" t="n">
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>10137418.96457929</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="N15" s="6" t="n">
         <v>28678.38779133129</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="O15" s="6" t="n">
         <v>28678.38779133129</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P15" s="6" t="n">
         <v>4011.649764621767</v>
       </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1785,46 +1897,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>19999704.07519871</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>19999614.04838496</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="I16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="n">
+      <c r="I16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>-90.02681374918072</v>
       </c>
-      <c r="K16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7" t="n">
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>8811902.569257861</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="N16" s="6" t="n">
         <v>24928.55034832756</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="6" t="n">
         <v>24928.55034832756</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>-25018.57716207674</v>
       </c>
-      <c r="Q16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -1844,48 +1956,46 @@
           <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="7" t="n">
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6" t="n">
         <v>-9486.73068036744</v>
       </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="n">
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="n">
         <v>9486.73068036744</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -1915,46 +2025,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>50000607.68881255</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>50000220.37445297</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>-387.3143595855997</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7" t="n">
+      <c r="I18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>29635839.11430195</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7" t="n">
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="P18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7" t="n">
+      <c r="P18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6" t="n">
         <v>29635839.11430195</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -1984,49 +2094,48 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>40137.360529</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>1.367235</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>-40135.993294</v>
       </c>
-      <c r="H19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="7" t="n">
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>255930.9107552667</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="6" t="n">
         <v>724.0191938474095</v>
       </c>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="6" t="n">
         <v>724.0191938474095</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P19" s="6" t="n">
         <v>-724.0191938474095</v>
       </c>
-      <c r="Q19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2049,49 +2158,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="n">
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>1468.586624033333</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n">
         <v>4.154577891704791</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="6" t="n">
         <v>4.154577891704791</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>-4.154577891704791</v>
       </c>
-      <c r="Q20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2114,49 +2222,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>2.03</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>-0.05</v>
       </c>
-      <c r="H21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="7" t="n">
+      <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>962.4027748666666</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="6" t="n">
         <v>2.722602280276279</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="6" t="n">
         <v>2.722602280276279</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>-2.722602280276279</v>
       </c>
-      <c r="Q21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2179,49 +2286,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>907.5387997189844</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>1091.224531135664</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="6" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="I22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="n">
+      <c r="I22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="n">
         <v>183.6857314166796</v>
       </c>
-      <c r="K22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="7" t="n">
+      <c r="K22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>907.5387997189844</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="6" t="n">
         <v>2.567394099519739</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="6" t="n">
         <v>2.567394099519739</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="P22" s="6" t="n">
         <v>181.1183373171599</v>
       </c>
-      <c r="Q22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="Q22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2244,49 +2350,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="7" t="n">
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>283.8972488542868</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="6" t="n">
         <v>0.8031349423342302</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <v>0.8031349423342302</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>-0.8031349423342302</v>
       </c>
-      <c r="Q23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="Q23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2309,49 +2414,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="7" t="n">
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>178.3188656666667</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="6" t="n">
         <v>0.5044575545281519</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="6" t="n">
         <v>0.5044575545281519</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>-0.5044575545281519</v>
       </c>
-      <c r="Q24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2374,49 +2478,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>3039.891609</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="n">
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
         <v>-3039.891609</v>
       </c>
-      <c r="H25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="7" t="n">
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>146.7413761333333</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="N25" s="6" t="n">
         <v>0.415125990598731</v>
       </c>
-      <c r="O25" s="7" t="n">
+      <c r="O25" s="6" t="n">
         <v>0.415125990598731</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="P25" s="6" t="n">
         <v>-0.415125990598731</v>
       </c>
-      <c r="Q25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="Q25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2439,49 +2542,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>100.8102461380194</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>101.2017120368429</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="I26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7" t="n">
+      <c r="I26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="n">
         <v>0.3914658988234815</v>
       </c>
-      <c r="K26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7" t="n">
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>100.8102461380194</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="N26" s="6" t="n">
         <v>0.2851885023384411</v>
       </c>
-      <c r="O26" s="7" t="n">
+      <c r="O26" s="6" t="n">
         <v>0.2851885023384411</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>0.1062773964850405</v>
       </c>
-      <c r="Q26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="Q26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2504,49 +2606,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="6" t="n">
         <v>22.16728989737678</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>22.1674058733521</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="6" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="I27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7" t="n">
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>0.0001159759753238479</v>
       </c>
-      <c r="K27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7" t="n">
+      <c r="K27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>22.16728989737678</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="6" t="n">
         <v>0.06271045304343052</v>
       </c>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="6" t="n">
         <v>0.06271045304343052</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P27" s="6" t="n">
         <v>-0.06259447706810667</v>
       </c>
-      <c r="Q27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="Q27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2569,49 +2670,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="6" t="n">
         <v>5.953731</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>5.971376</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>0.017645</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>0.017645</v>
       </c>
-      <c r="I28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="n">
+      <c r="I28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="n">
         <v>0.017645</v>
       </c>
-      <c r="K28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7" t="n">
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>5.953731</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="6" t="n">
         <v>0.01684288742724925</v>
       </c>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="6" t="n">
         <v>0.01684288742724925</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="P28" s="6" t="n">
         <v>0.0008021125727507489</v>
       </c>
-      <c r="Q28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="Q28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2634,49 +2734,48 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>3.882840172509015</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>3.88330436564981</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="6" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="7" t="n">
+      <c r="I29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6" t="n">
         <v>0.0004641931407952366</v>
       </c>
-      <c r="K29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="n">
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>3.882840172509015</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="N29" s="6" t="n">
         <v>0.01098441295442646</v>
       </c>
-      <c r="O29" s="7" t="n">
+      <c r="O29" s="6" t="n">
         <v>0.01098441295442646</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P29" s="6" t="n">
         <v>-0.01052021981363122</v>
       </c>
-      <c r="Q29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2699,46 +2798,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>0.8392619557395509</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>0.009413515804298108</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="6" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="6" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="6" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="6" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="6" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="M30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="7" t="n">
+      <c r="M30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="P30" s="7" t="n">
+      <c r="P30" s="6" t="n">
         <v>0.0007130876369377308</v>
       </c>
-      <c r="Q30" s="7" t="n">
+      <c r="Q30" s="6" t="n">
         <v>0.8298484399352527</v>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="R30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
@@ -2768,49 +2867,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="6" t="n">
         <v>1.762330143465235</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>1.766602634051488</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="6" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="7" t="n">
+      <c r="I31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>0.004272490586253392</v>
       </c>
-      <c r="K31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="7" t="n">
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>1.762330143465235</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="N31" s="6" t="n">
         <v>0.004985567573683288</v>
       </c>
-      <c r="O31" s="7" t="n">
+      <c r="O31" s="6" t="n">
         <v>0.004985567573683288</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P31" s="6" t="n">
         <v>-0.0007130769874298964</v>
       </c>
-      <c r="Q31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2833,49 +2931,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="6" t="n">
         <v>0.156574</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>0.157194</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>0.00062</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>0.00062</v>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="n">
+      <c r="I32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="6" t="n">
         <v>0.00062</v>
       </c>
-      <c r="K32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="n">
+      <c r="K32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>0.156574</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="N32" s="6" t="n">
         <v>0.0004429421241964281</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O32" s="6" t="n">
         <v>0.0004429421241964281</v>
       </c>
-      <c r="P32" s="7" t="n">
+      <c r="P32" s="6" t="n">
         <v>0.0001770578758035719</v>
       </c>
-      <c r="Q32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2898,49 +2995,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="7" t="n">
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>0.1180892666666667</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="6" t="n">
         <v>0.0003340702199735064</v>
       </c>
-      <c r="O33" s="7" t="n">
+      <c r="O33" s="6" t="n">
         <v>0.0003340702199735064</v>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P33" s="6" t="n">
         <v>-0.0003340702199735064</v>
       </c>
-      <c r="Q33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2963,49 +3059,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="6" t="n">
         <v>0.058479</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>0.058664</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>0.000185</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>0.000185</v>
       </c>
-      <c r="I34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="7" t="n">
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>0.000185</v>
       </c>
-      <c r="K34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="n">
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>0.058479</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.0001654349539571252</v>
       </c>
-      <c r="O34" s="7" t="n">
+      <c r="O34" s="6" t="n">
         <v>0.0001654349539571252</v>
       </c>
-      <c r="P34" s="7" t="n">
+      <c r="P34" s="6" t="n">
         <v>1.95650460428748e-05</v>
       </c>
-      <c r="Q34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="Q34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3028,49 +3123,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="6" t="n">
         <v>0.006402</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>0.006417</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="6" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="I35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="7" t="n">
+      <c r="I35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="n">
         <v>1.5e-05</v>
       </c>
-      <c r="K35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="7" t="n">
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>0.006402</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="N35" s="6" t="n">
         <v>1.811102404681194e-05</v>
       </c>
-      <c r="O35" s="7" t="n">
+      <c r="O35" s="6" t="n">
         <v>1.811102404681194e-05</v>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="P35" s="6" t="n">
         <v>-3.111024046811941e-06</v>
       </c>
-      <c r="Q35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="Q35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3093,49 +3187,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="6" t="n">
         <v>0.005749186661712982</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>0.005749998097404683</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="6" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="I36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="7" t="n">
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
         <v>8.11435691701e-07</v>
       </c>
-      <c r="K36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="7" t="n">
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>0.005749186661712982</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="N36" s="6" t="n">
         <v>1.626423896905565e-05</v>
       </c>
-      <c r="O36" s="7" t="n">
+      <c r="O36" s="6" t="n">
         <v>1.626423896905565e-05</v>
       </c>
-      <c r="P36" s="7" t="n">
+      <c r="P36" s="6" t="n">
         <v>-1.545280327735465e-05</v>
       </c>
-      <c r="Q36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3158,49 +3251,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="6" t="n">
         <v>0.001719</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="6" t="n">
         <v>0.001724</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="6" t="n">
         <v>5e-06</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="6" t="n">
         <v>5e-06</v>
       </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="7" t="n">
+      <c r="I37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6" t="n">
         <v>5e-06</v>
       </c>
-      <c r="K37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="7" t="n">
+      <c r="K37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>0.001719</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N37" s="6" t="n">
         <v>4.862988181266749e-06</v>
       </c>
-      <c r="O37" s="7" t="n">
+      <c r="O37" s="6" t="n">
         <v>4.862988181266749e-06</v>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P37" s="6" t="n">
         <v>1.37011818733251e-07</v>
       </c>
-      <c r="Q37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="Q37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3223,49 +3315,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="6" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="G38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="7" t="n">
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>0.001240144670509943</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="N38" s="6" t="n">
         <v>3.508323953316347e-06</v>
       </c>
-      <c r="O38" s="7" t="n">
+      <c r="O38" s="6" t="n">
         <v>3.508323953316347e-06</v>
       </c>
-      <c r="P38" s="7" t="n">
+      <c r="P38" s="6" t="n">
         <v>-3.508323953316347e-06</v>
       </c>
-      <c r="Q38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="Q38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3288,49 +3379,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="6" t="n">
         <v>0.000522802561158111</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>0.000523116949023306</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="6" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="7" t="n">
+      <c r="I39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6" t="n">
         <v>3.14387865195e-07</v>
       </c>
-      <c r="K39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="7" t="n">
+      <c r="K39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>0.000522802561158111</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N39" s="6" t="n">
         <v>1.47898934034199e-06</v>
       </c>
-      <c r="O39" s="7" t="n">
+      <c r="O39" s="6" t="n">
         <v>1.47898934034199e-06</v>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P39" s="6" t="n">
         <v>-1.16460147514699e-06</v>
       </c>
-      <c r="Q39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3353,49 +3443,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="6" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="7" t="n">
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>7.4896275897803e-05</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N40" s="6" t="n">
         <v>2.118788275229259e-07</v>
       </c>
-      <c r="O40" s="7" t="n">
+      <c r="O40" s="6" t="n">
         <v>2.118788275229259e-07</v>
       </c>
-      <c r="P40" s="7" t="n">
+      <c r="P40" s="6" t="n">
         <v>-2.118788275229259e-07</v>
       </c>
-      <c r="Q40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3418,49 +3507,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="6" t="n">
         <v>1.18094e-06</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>1.185745e-06</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="6" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="6" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="7" t="n">
+      <c r="I41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6" t="n">
         <v>4.805e-09</v>
       </c>
-      <c r="K41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="7" t="n">
+      <c r="K41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>1.18094e-06</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="7" t="n">
+      <c r="N41" s="6" t="n">
         <v>3.340836104005325e-09</v>
       </c>
-      <c r="O41" s="7" t="n">
+      <c r="O41" s="6" t="n">
         <v>3.340836104005325e-09</v>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P41" s="6" t="n">
         <v>1.464163895994674e-09</v>
       </c>
-      <c r="Q41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3483,49 +3571,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="8" t="n">
+      <c r="E42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="N42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3548,49 +3635,48 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="8" t="n">
+      <c r="E43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
+      <c r="N43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3613,49 +3699,48 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="8" t="n">
+      <c r="E44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="N44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3678,46 +3763,46 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="7" t="n">
+      <c r="E45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
@@ -3747,49 +3832,48 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="8" t="n">
+      <c r="E46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="N46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3812,49 +3896,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="7" t="n">
+      <c r="E47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
         <v>984135</v>
       </c>
-      <c r="I47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="7" t="n">
+      <c r="I47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="6" t="n">
         <v>984135</v>
       </c>
-      <c r="K47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="8" t="n">
+      <c r="K47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="7" t="n">
+      <c r="N47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="6" t="n">
         <v>984135</v>
       </c>
-      <c r="Q47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="Q47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3877,49 +3960,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="8" t="n">
+      <c r="E48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="N48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3942,46 +4024,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="7" t="n">
+      <c r="E49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
@@ -4011,49 +4093,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="8" t="n">
+      <c r="E50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="N50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4076,46 +4157,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="n">
+      <c r="E51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6" t="n">
         <v>1778866.820550583</v>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="6" t="n">
         <v>1778866.820550583</v>
       </c>
-      <c r="H51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="7" t="n">
+      <c r="H51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="6" t="n">
         <v>296477.8034250973</v>
       </c>
-      <c r="M51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="7" t="n">
+      <c r="M51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6" t="n">
         <v>296477.8034250973</v>
       </c>
-      <c r="R51" s="7" t="n">
+      <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
@@ -4145,49 +4226,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="8" t="n">
+      <c r="E52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
+      <c r="N52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4210,46 +4290,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E53" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="6" t="n">
         <v>99326272.7790609</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="6" t="n">
         <v>9326272.7790609</v>
       </c>
-      <c r="H53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="7" t="n">
+      <c r="H53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="6" t="n">
         <v>91554378.79651015</v>
       </c>
-      <c r="M53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="7" t="n">
+      <c r="M53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="6" t="n">
         <v>91554378.79651015</v>
       </c>
-      <c r="R53" s="7" t="n">
+      <c r="R53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
@@ -4279,49 +4359,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="8" t="n">
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4344,46 +4423,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="7" t="n">
+      <c r="E55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
@@ -4413,49 +4492,48 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="8" t="n">
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4478,46 +4556,46 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="7" t="n">
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
@@ -4547,49 +4625,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="8" t="n">
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr"/>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4602,48 +4679,46 @@
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="7" t="n">
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
@@ -4653,39 +4728,39 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
@@ -4712,10 +4787,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="6" t="n">
         <v>309261582.801972</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>300586529.588196</v>
       </c>
     </row>
@@ -4740,10 +4815,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" s="6" t="n">
         <v>367530003.125796</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="6" t="n">
         <v>447000057.62485</v>
       </c>
     </row>
@@ -4768,10 +4843,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="6" t="n">
         <v>230753.271254</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="6" t="n">
         <v>31037.026892</v>
       </c>
     </row>
@@ -4796,24 +4871,20 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="6" t="n">
         <v>9475726.147763001</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>8678568.642703</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" s="10" t="n">
+      <c r="F67" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4822,7 +4893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4843,19 +4914,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -4867,7 +4938,7 @@
           <t>Time-weighted utilized</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="6" t="n">
         <v>2687080256.868631</v>
       </c>
     </row>
@@ -4877,7 +4948,7 @@
           <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>1000000000</v>
       </c>
     </row>
@@ -4887,7 +4958,7 @@
           <t xml:space="preserve">  — excess (full base-rate tranche)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>1687080256.868631</v>
       </c>
     </row>
@@ -4897,7 +4968,7 @@
           <t>Base rate (BR_apr = apy_to_apr(SSR,12) + spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>0.03737387237537716</v>
       </c>
     </row>
@@ -4907,8 +4978,8 @@
           <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0.03748</v>
+      <c r="B9" s="7" t="n">
+        <v>0.03748666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -4917,37 +4988,37 @@
           <t>Subsidised rate (BR*), period avg</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>0.03703300982840613</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Effective blended rate charged</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.03724932945187823</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Diff vs base rate (bps)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="11" t="n">
         <v>-1.245429234989398</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Subsidy benefit to prime (USD)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>27506.04089315324</v>
       </c>
     </row>
@@ -4957,7 +5028,7 @@
           <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="n">
         <v>8254240.650624979</v>
       </c>
     </row>
@@ -4967,32 +5038,32 @@
           <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="n">
         <v>8226734.609731826</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  = subsidy benefit</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>27506.04089315324</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Avg balance</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>CoF (USD)</t>
         </is>
@@ -5004,10 +5075,10 @@
           <t>Subsidised (first $1B)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="6" t="n">
         <v>1000000000</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>3043809.026992285</v>
       </c>
     </row>
@@ -5017,20 +5088,20 @@
           <t>Excess (&gt; cap)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="6" t="n">
         <v>1687080256.868631</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>5182925.58273954</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -5042,7 +5113,7 @@
           <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="3" t="n">
         <v>8214792.081688168</v>
       </c>
     </row>
@@ -5052,7 +5123,7 @@
           <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="3" t="n">
         <v>3875.849924106662</v>
       </c>
     </row>
@@ -5062,24 +5133,24 @@
           <t>equals sky_revenue (total Sky take this month)</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="3" t="n">
         <v>8218667.931612275</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="3" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>
@@ -5089,7 +5160,7 @@
           <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="3" t="n">
         <v>8214792.081688168</v>
       </c>
     </row>
@@ -5099,34 +5170,34 @@
           <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="3" t="n">
         <v>-2042729.752441128</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="3" t="n">
         <v>11942.52804365823</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -5150,7 +5221,7 @@
           <t>cap_usd</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="6" t="n">
         <v>1000000000</v>
       </c>
     </row>
@@ -5201,7 +5272,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
@@ -5213,7 +5284,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). Daily charge = utilized_d x base_apr / 365 — no intra-month compounding.</t>
         </is>
@@ -5224,7 +5295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5253,52 +5324,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Cap (USD)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Active?</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>actual_revenue</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>sd_revenue (to Sky)</t>
         </is>
@@ -5315,7 +5386,6 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>2025-10-30</t>
@@ -5341,10 +5411,10 @@
           <t>USTB on Eth</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5359,7 +5429,6 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>2025-11-13</t>
@@ -5385,10 +5454,10 @@
           <t>USDT in sUSDS/USDT Curve</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.008700428167360377</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.008700428167360377</v>
       </c>
     </row>
@@ -5403,7 +5472,6 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-02-01</t>
@@ -5429,10 +5497,10 @@
           <t>USDT in USDT/USDS Uniswap V4</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="6" t="n">
         <v>3875.841223678495</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="6" t="n">
         <v>3875.841223678495</v>
       </c>
     </row>
@@ -5441,7 +5509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5475,83 +5543,83 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). sub_apr applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apr.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>cum_debt</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>− ALM idle</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>− PSM USDS</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>− SDE NAV</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>− Curve idle</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>− Lending idle</t>
         </is>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f> utilized</f>
         <v/>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>SSR APY</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>base APR</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>T (months)</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>ref_rate APR</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>sub APR</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>daily Sky charge</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>daily Sky charge (gross on cum_debt)</t>
         </is>
@@ -5563,46 +5631,46 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>2906763421.062537</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>10787782.10438779</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="6" t="n">
         <v>46184868.72615942</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>66134186.85567197</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>321674890.8327978</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="6" t="n">
         <v>2371981692.54352</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.03519999850777533</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="7" t="n">
         <v>0.03664455749990904</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="7" t="n">
         <v>0.0366</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>0.03661485249996968</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="3" t="n">
         <v>238056.2041676801</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="3" t="n">
         <v>291746.1762241619</v>
       </c>
     </row>
@@ -5612,46 +5680,46 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>2890435099.376095</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>10783394.72011987</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="6" t="n">
         <v>42941079.57266001</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>73873920.36187291</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="6" t="n">
         <v>316351823.6700861</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="6" t="n">
         <v>2356484881.051357</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.03519999850777533</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="7" t="n">
         <v>0.03664455749990904</v>
       </c>
       <c r="K7" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="7" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>0.03654818583330301</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="3" t="n">
         <v>236317.7371362924</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="3" t="n">
         <v>289924.2288554427</v>
       </c>
     </row>
@@ -5661,46 +5729,46 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>2967508830.591976</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>10781425.15239475</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="6" t="n">
         <v>33590920.91094027</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>85998904.9177648</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>336540318.0229259</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="6" t="n">
         <v>2410597261.58795</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="7" t="n">
         <v>0.0366</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>0.03687310577117104</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="3" t="n">
         <v>245634.7734358992</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="3" t="n">
         <v>302728.6110143323</v>
       </c>
     </row>
@@ -5710,46 +5778,46 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>2988013324.706798</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>10779506.1219177</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="6" t="n">
         <v>28343954.51391455</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="6" t="n">
         <v>88309100.01729183</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="6" t="n">
         <v>342696670.1153459</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="6" t="n">
         <v>2427884093.938328</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="L9" s="7" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="7" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="3" t="n">
         <v>247224.3482260297</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="3" t="n">
         <v>304648.0562334253</v>
       </c>
     </row>
@@ -5759,46 +5827,46 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>2928274110.318439</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>10777287.92069298</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="6" t="n">
         <v>33362192.54020159</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>82344906.19469523</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>327280160.0470022</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="6" t="n">
         <v>2384509563.615847</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="J10" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="7" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="7" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="3" t="n">
         <v>242777.648737094</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="3" t="n">
         <v>298523.6709751842</v>
       </c>
     </row>
@@ -5808,46 +5876,46 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <v>2956412327.73415</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>10787280.79874208</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>35799400.42037193</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>77757918.74799147</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>330059413.61901</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>2412008314.148035</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="7" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="7" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="3" t="n">
         <v>245596.7842765161</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="3" t="n">
         <v>301408.3638138557</v>
       </c>
     </row>
@@ -5857,46 +5925,46 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>3000452982.63504</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>10784103.99660763</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>39204009.08141842</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>73468764.68268934</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>341972638.172222</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>2445023466.702103</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="J12" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="7" t="n">
         <v>0.0365</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="7" t="n">
         <v>0.03680643910450437</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="3" t="n">
         <v>248981.4540561729</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="O12" s="3" t="n">
         <v>305923.3535136677</v>
       </c>
     </row>
@@ -5906,46 +5974,46 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="6" t="n">
         <v>2995839152.421766</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>10782756.13469957</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>37651547.86163576</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>77135483.14091809</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>345474185.8099677</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>2434795179.474545</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="7" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="7" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="3" t="n">
         <v>247750.2151739581</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="O13" s="3" t="n">
         <v>305267.7013398379</v>
       </c>
     </row>
@@ -5955,46 +6023,46 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="6" t="n">
         <v>3133651114.325167</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>10797020.24891723</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>40743786.39046462</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>74412072.93470116</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>383589267.5591224</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>2534108967.191961</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="7" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="7" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="3" t="n">
         <v>257931.7333553413</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="3" t="n">
         <v>319396.0014276766</v>
       </c>
     </row>
@@ -6004,46 +6072,46 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="6" t="n">
         <v>3227081891.544717</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>10846682.58683929</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>42457056.322888</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>75494030.84493366</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>421499085.0281916</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="6" t="n">
         <v>2586785036.761865</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="J15" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L15" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="3" t="n">
         <v>262966.717543647</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="O15" s="3" t="n">
         <v>328609.1043490277</v>
       </c>
     </row>
@@ -6053,46 +6121,46 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="6" t="n">
         <v>3297373641.594151</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>11051222.40951546</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>39392044.00456543</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>70852872.02856682</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>448108701.9685125</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>2637968801.182991</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="J16" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="L16" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="3" t="n">
         <v>268214.0093852202</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="3" t="n">
         <v>335815.3216082659</v>
       </c>
     </row>
@@ -6102,46 +6170,46 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="6" t="n">
         <v>3261296362.641112</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>10958189.66850853</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>38323346.1236461</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>74526830.75221506</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>439333902.4873285</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="6" t="n">
         <v>2608154093.609414</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K17" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="3" t="n">
         <v>265157.444992603</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="3" t="n">
         <v>332116.7266796306</v>
       </c>
     </row>
@@ -6151,46 +6219,46 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="6" t="n">
         <v>3271620408.368682</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>10967668.13417339</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>44209251.24223101</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>69262929.5670072</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>438574487.8959026</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>2618606071.529368</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="J18" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="3" t="n">
         <v>266228.9679469608</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="O18" s="3" t="n">
         <v>333175.1341948064</v>
       </c>
     </row>
@@ -6200,46 +6268,46 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="6" t="n">
         <v>3336773639.899233</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>11011831.47225842</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>38717183.1975746</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>74780064.69773053</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>459982093.6032678</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="6" t="n">
         <v>2662282466.928402</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J19" s="8" t="n">
+      <c r="J19" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L19" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="3" t="n">
         <v>270706.6142443497</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="O19" s="3" t="n">
         <v>339854.5573308132</v>
       </c>
     </row>
@@ -6249,46 +6317,46 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="6" t="n">
         <v>3408882342.468478</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>11013377.08004701</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>51464357.30621822</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>63078762.22766157</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>486544767.4335539</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="6" t="n">
         <v>2706781078.420998</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J20" s="8" t="n">
+      <c r="J20" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="7" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="7" t="n">
         <v>0.03673977243783771</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="3" t="n">
         <v>275633.8498519812</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="3" t="n">
         <v>347612.3429632451</v>
       </c>
     </row>
@@ -6298,46 +6366,46 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="6" t="n">
         <v>3472868914.590904</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>11015189.69398859</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>53285053.35791527</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>59219558.5191095</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>520256687.5533239</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="n">
         <v>2739092425.466567</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="J21" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="7" t="n">
         <v>0.0362</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="7" t="n">
         <v>0.03660643910450437</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="3" t="n">
         <v>278581.0696179863</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="O21" s="3" t="n">
         <v>353806.8649159018</v>
       </c>
     </row>
@@ -6347,46 +6415,46 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="6" t="n">
         <v>3532508643.580109</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>11015476.02521076</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>54701824.10007302</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>56533917.02449908</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>544096705.3514518</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="6" t="n">
         <v>2776160721.078874</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J22" s="8" t="n">
+      <c r="J22" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K22" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="7" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="3" t="n">
         <v>284608.3258503062</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="O22" s="3" t="n">
         <v>362148.1146489092</v>
       </c>
     </row>
@@ -6396,46 +6464,46 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="6" t="n">
         <v>3557227409.970616</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>11011283.2026294</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>39807184.62271105</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>75881936.86035079</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>547009412.1599061</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="6" t="n">
         <v>2793517593.125018</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J23" s="8" t="n">
+      <c r="J23" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="L23" s="7" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="3" t="n">
         <v>286387.7294192506</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="O23" s="3" t="n">
         <v>364682.2498904572</v>
       </c>
     </row>
@@ -6445,46 +6513,46 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="6" t="n">
         <v>3582188103.687335</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>11022797.04070983</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>42362026.83740311</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>69117035.89852072</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>555046298.1893152</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="6" t="n">
         <v>2814639945.721386</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="J24" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="L24" s="7" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="3" t="n">
         <v>288553.1650746243</v>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="O24" s="3" t="n">
         <v>367241.1872015567</v>
       </c>
     </row>
@@ -6494,46 +6562,46 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="6" t="n">
         <v>3615656122.574477</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>11021528.4331681</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>40669150.95574692</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>70044162.34119777</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>555099974.3238693</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="6" t="n">
         <v>2848821306.520495</v>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="J25" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="7" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="3" t="n">
         <v>292057.3929813354</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="O25" s="3" t="n">
         <v>370672.2842387968</v>
       </c>
     </row>
@@ -6543,46 +6611,46 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="6" t="n">
         <v>3668718424.821697</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>11017474.21178086</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>39640105.26414733</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>80565486.31273285</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>511522523.5145142</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>2935972835.518521</v>
       </c>
-      <c r="I26" s="8" t="n">
+      <c r="I26" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="7" t="n">
         <v>0.0385</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="3" t="n">
         <v>300992.0524825271</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="O26" s="3" t="n">
         <v>376112.1612940687</v>
       </c>
     </row>
@@ -6592,46 +6660,46 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="6" t="n">
         <v>3654567772.917019</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>11013549.04707003</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="6" t="n">
         <v>38195404.07725928</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>77310138.73431022</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>509580863.5732393</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="6" t="n">
         <v>2928467817.485141</v>
       </c>
-      <c r="I27" s="8" t="n">
+      <c r="I27" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J27" s="8" t="n">
+      <c r="J27" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K27" t="n">
         <v>8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="7" t="n">
         <v>0.0387</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="3" t="n">
         <v>300222.6479585964</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="O27" s="3" t="n">
         <v>374661.4551740298</v>
       </c>
     </row>
@@ -6641,46 +6709,46 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="6" t="n">
         <v>3613986960.44891</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>11024090.25538417</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="6" t="n">
         <v>38791154.5504749</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>77315744.47759701</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>489850897.9694406</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>2907005073.196013</v>
       </c>
-      <c r="I28" s="8" t="n">
+      <c r="I28" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J28" s="8" t="n">
+      <c r="J28" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K28" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="7" t="n">
         <v>0.0387</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="3" t="n">
         <v>298022.3157970248</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="O28" s="3" t="n">
         <v>370501.1639450316</v>
       </c>
     </row>
@@ -6690,46 +6758,46 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="6" t="n">
         <v>3562391445.516993</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>11106742.99290403</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>42557094.58933863</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>72747259.58101186</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>476137012.6093084</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="6" t="n">
         <v>2869843335.74443</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="J29" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="7" t="n">
         <v>0.0388</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="3" t="n">
         <v>294212.5436172377</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="O29" s="3" t="n">
         <v>365211.6599856028</v>
       </c>
     </row>
@@ -6739,46 +6807,46 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="6" t="n">
         <v>3562110063.464996</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>11105892.44404138</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>39434498.72772756</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>78636692.55074844</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>477489965.700973</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="6" t="n">
         <v>2865443014.041506</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I30" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="J30" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K30" t="n">
         <v>8</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L30" s="7" t="n">
         <v>0.039</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="3" t="n">
         <v>293761.4284553658</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="O30" s="3" t="n">
         <v>365182.8130697398</v>
       </c>
     </row>
@@ -6788,46 +6856,46 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="6" t="n">
         <v>3556747626.534367</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="6" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="6" t="n">
         <v>0.9981644656134642</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="6" t="n">
         <v>40058756.90344783</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>75811953.01965727</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>476178335.913344</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="6" t="n">
         <v>2863593440.100142</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K31" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="7" t="n">
         <v>0.039</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="3" t="n">
         <v>293571.8125808269</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="O31" s="3" t="n">
         <v>364633.0631270524</v>
       </c>
     </row>
@@ -6837,46 +6905,46 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="6" t="n">
         <v>3569305881.745206</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>348.044919387507</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="6" t="n">
         <v>40276114.07045595</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>77458558.38944019</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>478099948.9814835</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>2872365772.659295</v>
       </c>
-      <c r="I32" s="8" t="n">
+      <c r="I32" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J32" s="8" t="n">
+      <c r="J32" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="7" t="n">
         <v>0.039</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="3" t="n">
         <v>294471.1405140067</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="O32" s="3" t="n">
         <v>365920.51884387</v>
       </c>
     </row>
@@ -6886,46 +6954,46 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="6" t="n">
         <v>3607683503.927528</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>475.1354724600163</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="6" t="n">
         <v>49030490.46679787</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>66105314.46354181</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>489068699.5676167</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="6" t="n">
         <v>2902373384.694488</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J33" s="8" t="n">
+      <c r="J33" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="7" t="n">
         <v>0.039</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="3" t="n">
         <v>297547.4812169262</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="O33" s="3" t="n">
         <v>369854.9419183315</v>
       </c>
     </row>
@@ -6935,46 +7003,46 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="6" t="n">
         <v>3630529651.948061</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="6" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>39645.63435542155</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="6" t="n">
         <v>46729012.84603118</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>70493387.35718162</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>490680595.5793573</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>2921481870.931524</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J34" s="8" t="n">
+      <c r="J34" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K34" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="7" t="n">
         <v>0.0388</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="3" t="n">
         <v>299506.457956336</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="O34" s="3" t="n">
         <v>372197.098800994</v>
       </c>
     </row>
@@ -6984,71 +7052,59 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="6" t="n">
         <v>3686615117.414475</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="6" t="n">
         <v>101105139.5996115</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>125648.5335501426</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="6" t="n">
         <v>52072873.79227647</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>63718676.68799376</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>493934577.7121899</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="6" t="n">
         <v>2975658201.088854</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="7" t="n">
         <v>0.03600000425292382</v>
       </c>
-      <c r="J35" s="8" t="n">
+      <c r="J35" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
       <c r="K35" t="n">
         <v>8</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>0.0388</v>
-      </c>
-      <c r="M35" s="8" t="n">
+      <c r="L35" s="7" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="M35" s="7" t="n">
         <v>0.03741931731351311</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="3" t="n">
         <v>305060.54367973</v>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="O35" s="3" t="n">
         <v>377946.9065515799</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" s="13" t="n">
+      <c r="N37" s="12" t="n">
         <v>8226734.609731826</v>
       </c>
-      <c r="O37" s="13" t="n">
+      <c r="O37" s="12" t="n">
         <v>10257521.8341293</v>
       </c>
     </row>

--- a/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
+++ b/settlements/spark/2026-09/spark_settlement_september_2026.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Close status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Venues" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Revenue" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sky Direct" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Debt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,12 +91,6 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,144 +458,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="115" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>September 2026 close</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Official reference-rate coverage complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>calculation</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Reference-rate-only recalculation of saved independently validated monthly inputs; compared with September 30 API result</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>calculation_code_version</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>c32f25a7ef410eaaf9212b8f546f652c715dc7ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>daily_revision</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>08ed233241c4ed1750dde86085a7bc5a0fff028fd08db4b1ca091956c283f645</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>monthly_result_sha256</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>72d23df466c98cf2f45f1c0b72aefd1fc7c9c0579d306de41b4350994c4a95ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>daily_result_sha256</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>72d23df466c98cf2f45f1c0b72aefd1fc7c9c0579d306de41b4350994c4a95ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>comparison</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>all result fields match</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>distribution_rewards_workbook_sha256</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>17eee2ca39bd63e68e6d87097ede0007d8741e41cb9a7fceb017da713103b02e</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>distribution_rewards_code</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>1e9ecb2 (merged settle-dr-dune PR #27; finalized September snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>reference_rate_status</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>official coverage complete</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -636,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9011591.411259666</v>
+        <v>9231208.261150554</v>
       </c>
     </row>
     <row r="5">
@@ -660,8 +515,9 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>9820941.757440846</v>
+        <v>10040558.60733173</v>
       </c>
     </row>
     <row r="9">
@@ -697,6 +553,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
         <v>8218667.931612275</v>
       </c>
@@ -734,6 +591,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
         <v>10257521.8341293</v>
       </c>
@@ -767,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>9011591.411259666</v>
+        <v>9231208.261150554</v>
       </c>
     </row>
     <row r="23">
@@ -781,8 +639,9 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>617223.378874959</v>
+        <v>836840.2287658466</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01T15:36:03+00:00</t>
+          <t>2026-10-01T16:21:50+00:00</t>
         </is>
       </c>
     </row>
@@ -838,7 +697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1028,6 +887,7 @@
       <c r="R2" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1063,10 +923,10 @@
         <v>2113055.557198851</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>219616.8498908877</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2113055.557198851</v>
+        <v>2332672.407089739</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
@@ -1084,7 +944,7 @@
         <v>2040828.455379347</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>72227.10181950497</v>
+        <v>291843.9517103927</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>356306847.9377152</v>
@@ -1161,6 +1021,7 @@
       <c r="R4" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1225,6 +1086,7 @@
       <c r="R5" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1289,6 +1151,7 @@
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1422,6 +1285,7 @@
       <c r="R8" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1486,6 +1350,7 @@
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1619,6 +1484,7 @@
       <c r="R11" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1683,6 +1549,7 @@
       <c r="R12" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1747,6 +1614,7 @@
       <c r="R13" s="6" t="n">
         <v>2455.797363290793</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1811,6 +1679,7 @@
       <c r="R14" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1875,6 +1744,7 @@
       <c r="R15" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1956,6 +1826,8 @@
           <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
@@ -2136,6 +2008,7 @@
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2200,6 +2073,7 @@
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2264,6 +2138,7 @@
       <c r="R21" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2328,6 +2203,7 @@
       <c r="R22" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2392,6 +2268,7 @@
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2456,6 +2333,7 @@
       <c r="R24" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2520,6 +2398,7 @@
       <c r="R25" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2584,6 +2463,7 @@
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2648,6 +2528,7 @@
       <c r="R27" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2712,6 +2593,7 @@
       <c r="R28" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2776,6 +2658,7 @@
       <c r="R29" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2909,6 +2792,7 @@
       <c r="R31" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2973,6 +2857,7 @@
       <c r="R32" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3037,6 +2922,7 @@
       <c r="R33" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3101,6 +2987,7 @@
       <c r="R34" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3165,6 +3052,7 @@
       <c r="R35" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3229,6 +3117,7 @@
       <c r="R36" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3293,6 +3182,7 @@
       <c r="R37" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3357,6 +3247,7 @@
       <c r="R38" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3421,6 +3312,7 @@
       <c r="R39" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3485,6 +3377,7 @@
       <c r="R40" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3549,6 +3442,7 @@
       <c r="R41" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3613,6 +3507,7 @@
       <c r="R42" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3677,6 +3572,7 @@
       <c r="R43" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3741,6 +3637,7 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3874,6 +3771,7 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3938,6 +3836,7 @@
       <c r="R47" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4002,6 +3901,7 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4135,6 +4035,7 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4268,6 +4169,7 @@
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4401,6 +4303,7 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4534,6 +4437,7 @@
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4667,6 +4571,7 @@
       <c r="R58" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4679,6 +4584,8 @@
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="6" t="n">
         <v>0</v>
       </c>
@@ -4879,11 +4786,15 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr"/>
       <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" s="9" t="n">
         <v>0</v>
       </c>
@@ -4893,7 +4804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5295,7 +5206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5386,6 +5297,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>2025-10-30</t>
@@ -5429,6 +5341,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>2025-11-13</t>
@@ -5472,6 +5385,7 @@
           <t>fixed</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-02-01</t>
@@ -5509,7 +5423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7101,6 +7015,18 @@
           <t>Σ daily charges</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
         <v>8226734.609731826</v>
       </c>
